--- a/assets/data/excel/minionCards.xlsx
+++ b/assets/data/excel/minionCards.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T103"/>
+  <dimension ref="A1:U103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.83203125" customWidth="1" min="1" max="1"/>
@@ -571,6 +571,11 @@
           <t>fusionCount</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>portrait</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -673,6 +678,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -775,6 +785,11 @@
           <t>融合次数</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>立绘路径</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,6 +876,7 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -947,6 +963,7 @@
       <c r="T5" t="n">
         <v>0</v>
       </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1033,6 +1050,7 @@
       <c r="T6" t="n">
         <v>0</v>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1119,6 +1137,7 @@
       <c r="T7" t="n">
         <v>0</v>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1205,6 +1224,11 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM005.png</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1291,6 +1315,7 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1377,6 +1402,7 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1463,6 +1489,7 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1549,6 +1576,7 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1635,6 +1663,7 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1721,6 +1750,11 @@
       <c r="T14" t="n">
         <v>0</v>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM011.png</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1807,6 +1841,11 @@
       <c r="T15" t="n">
         <v>0</v>
       </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM012.png</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1893,6 +1932,11 @@
       <c r="T16" t="n">
         <v>0</v>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM013.png</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1979,6 +2023,7 @@
       <c r="T17" t="n">
         <v>0</v>
       </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2065,6 +2110,11 @@
       <c r="T18" t="n">
         <v>0</v>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM015.png</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2151,6 +2201,11 @@
       <c r="T19" t="n">
         <v>0</v>
       </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM016.png</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2237,6 +2292,7 @@
       <c r="T20" t="n">
         <v>0</v>
       </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2323,6 +2379,7 @@
       <c r="T21" t="n">
         <v>0</v>
       </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2409,6 +2466,7 @@
       <c r="T22" t="n">
         <v>0</v>
       </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2495,6 +2553,11 @@
       <c r="T23" t="n">
         <v>0</v>
       </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM020.png</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2581,6 +2644,7 @@
       <c r="T24" t="n">
         <v>0</v>
       </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2667,6 +2731,7 @@
       <c r="T25" t="n">
         <v>0</v>
       </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2753,6 +2818,7 @@
       <c r="T26" t="n">
         <v>0</v>
       </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2839,6 +2905,7 @@
       <c r="T27" t="n">
         <v>0</v>
       </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2925,6 +2992,7 @@
       <c r="T28" t="n">
         <v>0</v>
       </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3011,6 +3079,7 @@
       <c r="T29" t="n">
         <v>0</v>
       </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3097,6 +3166,7 @@
       <c r="T30" t="n">
         <v>0</v>
       </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3183,6 +3253,7 @@
       <c r="T31" t="n">
         <v>0</v>
       </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3269,6 +3340,7 @@
       <c r="T32" t="n">
         <v>0</v>
       </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3355,6 +3427,7 @@
       <c r="T33" t="n">
         <v>0</v>
       </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3441,6 +3514,7 @@
       <c r="T34" t="n">
         <v>0</v>
       </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3527,6 +3601,11 @@
       <c r="T35" t="n">
         <v>0</v>
       </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM032.png</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3613,6 +3692,11 @@
       <c r="T36" t="n">
         <v>0</v>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM033.png</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3699,6 +3783,7 @@
       <c r="T37" t="n">
         <v>0</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3785,6 +3870,11 @@
       <c r="T38" t="n">
         <v>0</v>
       </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM035.png</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3871,6 +3961,11 @@
       <c r="T39" t="n">
         <v>0</v>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM036.png</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3957,6 +4052,11 @@
       <c r="T40" t="n">
         <v>0</v>
       </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM037.png</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4043,6 +4143,7 @@
       <c r="T41" t="n">
         <v>0</v>
       </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4129,6 +4230,11 @@
       <c r="T42" t="n">
         <v>0</v>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM039.png</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4215,6 +4321,7 @@
       <c r="T43" t="n">
         <v>0</v>
       </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4301,6 +4408,7 @@
       <c r="T44" t="n">
         <v>0</v>
       </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4387,6 +4495,7 @@
       <c r="T45" t="n">
         <v>0</v>
       </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4473,6 +4582,11 @@
       <c r="T46" t="n">
         <v>0</v>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM043.png</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4559,6 +4673,11 @@
       <c r="T47" t="n">
         <v>0</v>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM044.png</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4645,6 +4764,7 @@
       <c r="T48" t="n">
         <v>0</v>
       </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4731,6 +4851,11 @@
       <c r="T49" t="n">
         <v>0</v>
       </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM046.png</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4817,6 +4942,7 @@
       <c r="T50" t="n">
         <v>0</v>
       </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4903,6 +5029,11 @@
       <c r="T51" t="n">
         <v>0</v>
       </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM048.png</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4989,6 +5120,11 @@
       <c r="T52" t="n">
         <v>0</v>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM049.png</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5075,6 +5211,7 @@
       <c r="T53" t="n">
         <v>0</v>
       </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5161,6 +5298,7 @@
       <c r="T54" t="n">
         <v>0</v>
       </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5247,6 +5385,7 @@
       <c r="T55" t="n">
         <v>0</v>
       </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5333,6 +5472,11 @@
       <c r="T56" t="n">
         <v>0</v>
       </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM053.png</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5419,6 +5563,7 @@
       <c r="T57" t="n">
         <v>0</v>
       </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5505,6 +5650,7 @@
       <c r="T58" t="n">
         <v>0</v>
       </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5591,6 +5737,7 @@
       <c r="T59" t="n">
         <v>0</v>
       </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5677,6 +5824,11 @@
       <c r="T60" t="n">
         <v>0</v>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM057.png</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5763,6 +5915,11 @@
       <c r="T61" t="n">
         <v>0</v>
       </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM058.png</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5849,6 +6006,7 @@
       <c r="T62" t="n">
         <v>0</v>
       </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5935,6 +6093,7 @@
       <c r="T63" t="n">
         <v>0</v>
       </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6021,6 +6180,7 @@
       <c r="T64" t="n">
         <v>0</v>
       </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6107,6 +6267,7 @@
       <c r="T65" t="n">
         <v>0</v>
       </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6193,6 +6354,7 @@
       <c r="T66" t="n">
         <v>0</v>
       </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6279,6 +6441,7 @@
       <c r="T67" t="n">
         <v>0</v>
       </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6365,6 +6528,7 @@
       <c r="T68" t="n">
         <v>0</v>
       </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6451,6 +6615,7 @@
       <c r="T69" t="n">
         <v>0</v>
       </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6537,6 +6702,7 @@
       <c r="T70" t="n">
         <v>0</v>
       </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6623,6 +6789,7 @@
       <c r="T71" t="n">
         <v>0</v>
       </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6709,6 +6876,7 @@
       <c r="T72" t="n">
         <v>0</v>
       </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6795,6 +6963,7 @@
       <c r="T73" t="n">
         <v>0</v>
       </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6881,6 +7050,7 @@
       <c r="T74" t="n">
         <v>0</v>
       </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6967,6 +7137,7 @@
       <c r="T75" t="n">
         <v>0</v>
       </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7053,6 +7224,7 @@
       <c r="T76" t="n">
         <v>0</v>
       </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7139,6 +7311,7 @@
       <c r="T77" t="n">
         <v>0</v>
       </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7225,6 +7398,7 @@
       <c r="T78" t="n">
         <v>0</v>
       </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7311,6 +7485,7 @@
       <c r="T79" t="n">
         <v>0</v>
       </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7397,6 +7572,7 @@
       <c r="T80" t="n">
         <v>0</v>
       </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7483,6 +7659,7 @@
       <c r="T81" t="n">
         <v>0</v>
       </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7569,6 +7746,7 @@
       <c r="T82" t="n">
         <v>0</v>
       </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7655,6 +7833,7 @@
       <c r="T83" t="n">
         <v>0</v>
       </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7741,6 +7920,7 @@
       <c r="T84" t="n">
         <v>0</v>
       </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7827,6 +8007,7 @@
       <c r="T85" t="n">
         <v>0</v>
       </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7913,6 +8094,7 @@
       <c r="T86" t="n">
         <v>0</v>
       </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7999,6 +8181,7 @@
       <c r="T87" t="n">
         <v>0</v>
       </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8085,6 +8268,7 @@
       <c r="T88" t="n">
         <v>0</v>
       </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8171,6 +8355,7 @@
       <c r="T89" t="n">
         <v>0</v>
       </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8257,6 +8442,7 @@
       <c r="T90" t="n">
         <v>0</v>
       </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8343,6 +8529,7 @@
       <c r="T91" t="n">
         <v>0</v>
       </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8429,6 +8616,7 @@
       <c r="T92" t="n">
         <v>0</v>
       </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8515,6 +8703,7 @@
       <c r="T93" t="n">
         <v>0</v>
       </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8601,6 +8790,7 @@
       <c r="T94" t="n">
         <v>0</v>
       </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8687,6 +8877,7 @@
       <c r="T95" t="n">
         <v>0</v>
       </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8773,6 +8964,7 @@
       <c r="T96" t="n">
         <v>0</v>
       </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8859,6 +9051,7 @@
       <c r="T97" t="n">
         <v>0</v>
       </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8945,6 +9138,11 @@
       <c r="T98" t="n">
         <v>0</v>
       </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>characters/fusion/FM095.png</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9031,6 +9229,7 @@
       <c r="T99" t="n">
         <v>0</v>
       </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9117,6 +9316,7 @@
       <c r="T100" t="n">
         <v>0</v>
       </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9203,6 +9403,7 @@
       <c r="T101" t="n">
         <v>0</v>
       </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9289,6 +9490,7 @@
       <c r="T102" t="n">
         <v>0</v>
       </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9375,6 +9577,7 @@
       <c r="T103" t="n">
         <v>0</v>
       </c>
+      <c r="U103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
